--- a/Proyecto/Planificación.xlsx
+++ b/Proyecto/Planificación.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\OneDrive\Escritorio\Seminario avanzado PC\IPD_439_Workspaces\Avances\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\OneDrive\Escritorio\Seminario avanzado PC\IPD_439_Workspaces\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530104F8-B9B3-441C-9FDD-57736D404F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926AB89A-1735-4D36-B5FE-9BBBF4A86F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Estado</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Informe Final</t>
-  </si>
-  <si>
-    <t>(Ambas) Caracteristicas generales</t>
   </si>
   <si>
     <t>(Ambas) Offset y ganancia</t>
@@ -132,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,13 +161,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00FF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -604,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -735,9 +725,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -804,9 +791,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -834,18 +818,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,6 +832,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -882,19 +875,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1216,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BDEEE7-3BB4-49F6-AD6F-6EF6AD0D1C49}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
@@ -1228,27 +1230,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91"/>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="93" t="s">
+      <c r="A1" s="92"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="93" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="93" t="s">
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="95"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -1298,7 +1300,7 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="85" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -1307,8 +1309,8 @@
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="81"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16"/>
       <c r="H3" s="15"/>
@@ -1319,25 +1321,25 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="16"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
       <c r="U3" s="27"/>
       <c r="V3" s="27"/>
       <c r="W3" s="27"/>
     </row>
     <row r="4" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+        <v>2</v>
+      </c>
+      <c r="D4" s="42"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="32"/>
       <c r="H4" s="31"/>
       <c r="I4" s="30"/>
@@ -1356,7 +1358,7 @@
       <c r="W4" s="27"/>
     </row>
     <row r="5" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="88"/>
+      <c r="A5" s="89"/>
       <c r="B5" s="28" t="s">
         <v>16</v>
       </c>
@@ -1364,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="42"/>
-      <c r="E5" s="52"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="30"/>
       <c r="G5" s="32"/>
       <c r="H5" s="31"/>
@@ -1384,7 +1386,7 @@
       <c r="W5" s="27"/>
     </row>
     <row r="6" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
+      <c r="A6" s="89"/>
       <c r="B6" s="18" t="s">
         <v>12</v>
       </c>
@@ -1392,7 +1394,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="43"/>
-      <c r="E6" s="46"/>
+      <c r="E6" s="45"/>
       <c r="F6" s="8"/>
       <c r="G6" s="14"/>
       <c r="H6" s="12"/>
@@ -1408,71 +1410,71 @@
       <c r="W6" s="27"/>
     </row>
     <row r="7" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="25" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
+        <v>3</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
       <c r="K7" s="33"/>
       <c r="L7" s="38"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
       <c r="O7" s="33"/>
       <c r="U7" s="27"/>
       <c r="V7" s="27"/>
       <c r="W7" s="27"/>
     </row>
     <row r="8" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
+      <c r="A8" s="89"/>
       <c r="B8" s="40" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="94"/>
       <c r="G8" s="41"/>
       <c r="H8" s="39"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="73"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="71"/>
       <c r="L8" s="39"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
       <c r="O8" s="41"/>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
       <c r="W8" s="27"/>
     </row>
     <row r="9" spans="1:23" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
+      <c r="A9" s="89"/>
       <c r="B9" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
       <c r="G9" s="5"/>
       <c r="H9" s="35"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
       <c r="K9" s="5"/>
       <c r="L9" s="35"/>
-      <c r="M9" s="46"/>
+      <c r="M9" s="45"/>
       <c r="N9" s="23"/>
       <c r="O9" s="22"/>
       <c r="U9" s="27"/>
@@ -1480,50 +1482,50 @@
       <c r="W9" s="27"/>
     </row>
     <row r="10" spans="1:23" s="2" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="86"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="28" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
       <c r="G10" s="29"/>
       <c r="H10" s="37"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="29"/>
       <c r="L10" s="37"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
       <c r="O10" s="29"/>
       <c r="U10" s="27"/>
       <c r="V10" s="27"/>
       <c r="W10" s="27"/>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="85" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
       <c r="G11" s="4"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
       <c r="K11" s="4"/>
       <c r="L11" s="34"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
       <c r="O11" s="4"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -1534,24 +1536,24 @@
       <c r="W11" s="27"/>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85"/>
-      <c r="B12" s="18" t="s">
-        <v>15</v>
+      <c r="A12" s="86"/>
+      <c r="B12" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="5"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="100"/>
       <c r="H12" s="35"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
       <c r="K12" s="5"/>
       <c r="L12" s="35"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
       <c r="O12" s="5"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -1562,25 +1564,25 @@
       <c r="W12" s="27"/>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="5"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="29"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
@@ -1590,24 +1592,24 @@
       <c r="W13" s="27"/>
     </row>
     <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="74" t="s">
-        <v>22</v>
+      <c r="A14" s="87"/>
+      <c r="B14" s="72" t="s">
+        <v>24</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="61"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="37"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="29"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67"/>
       <c r="L14" s="37"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
       <c r="O14" s="29"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -1617,26 +1619,26 @@
       <c r="V14" s="27"/>
       <c r="W14" s="27"/>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="74" t="s">
+    <row r="15" spans="1:23" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="88"/>
+      <c r="B15" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="61"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="29"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="7"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
@@ -1645,26 +1647,28 @@
       <c r="V15" s="27"/>
       <c r="W15" s="27"/>
     </row>
-    <row r="16" spans="1:23" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="87"/>
-      <c r="B16" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="7" t="s">
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="7"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="4"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
@@ -1673,139 +1677,130 @@
       <c r="V16" s="27"/>
       <c r="W16" s="27"/>
     </row>
-    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="4"/>
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="90"/>
+      <c r="B17" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="47"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="33"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-    </row>
-    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="90"/>
       <c r="B18" s="25" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
       <c r="G18" s="33"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="49"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="48"/>
       <c r="K18" s="33"/>
       <c r="L18" s="38"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
       <c r="O18" s="33"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
-      <c r="B19" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="26" t="s">
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="86"/>
+      <c r="B19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="33"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="59"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="85"/>
-      <c r="B20" s="18" t="s">
+    <row r="20" spans="1:20" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="88"/>
+      <c r="B20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="54"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="60"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="62"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="1:23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="87"/>
-      <c r="B21" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="63"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="90"/>
-      <c r="B22" s="76"/>
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="91"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="63"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="91"/>
+      <c r="B22" s="74"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1819,14 +1814,14 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="64"/>
-    </row>
-    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="90"/>
-      <c r="B23" s="76"/>
+      <c r="Q22" s="63"/>
+      <c r="R22" s="63"/>
+      <c r="S22" s="63"/>
+      <c r="T22" s="63"/>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="91"/>
+      <c r="B23" s="74"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1840,14 +1835,14 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-    </row>
-    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="90"/>
-      <c r="B24" s="76"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+    </row>
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="91"/>
+      <c r="B24" s="74"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1863,55 +1858,34 @@
       <c r="O24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+      <c r="S24" s="79"/>
       <c r="T24" s="2"/>
     </row>
-    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="90"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="83"/>
+      <c r="S25" s="2"/>
       <c r="T25" s="2"/>
     </row>
-    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
     </row>
-    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="L1:O1"/>
-    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A11:A15"/>
     <mergeCell ref="A3:A10"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C25">
+  <conditionalFormatting sqref="C3:C24">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="En pausa">
       <formula>NOT(ISERROR(SEARCH("En pausa",C3)))</formula>
     </cfRule>
